--- a/문서함/기획/카드/카드.xlsx
+++ b/문서함/기획/카드/카드.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="150">
   <si>
     <t>이름</t>
   </si>
@@ -184,6 +184,9 @@
     <t>N 턴 동안 손패 카드 중 랜덤으로 소모 마나(코스트) 1 증가</t>
   </si>
   <si>
+    <t>번호</t>
+  </si>
+  <si>
     <t>카드 이름</t>
   </si>
   <si>
@@ -346,6 +349,45 @@
     <t>[인접 2칸] 내에 적을 견제합니다. 대상에게 [고립 1]과 [다음 카드 인접 카드 강화], 4 피해를 줍니다.</t>
   </si>
   <si>
+    <t>낡은 방패</t>
+  </si>
+  <si>
+    <t>기술</t>
+  </si>
+  <si>
+    <t>일반</t>
+  </si>
+  <si>
+    <t>방어도 5</t>
+  </si>
+  <si>
+    <t>방어도 5를 얻습니다.</t>
+  </si>
+  <si>
+    <t>무기 교체</t>
+  </si>
+  <si>
+    <t>시동</t>
+  </si>
+  <si>
+    <t>방어도 4</t>
+  </si>
+  <si>
+    <t>방어도 4를 얻고 이번 전투에서 사용한 특수 카드 1장을 덱으로 가져옵니다.</t>
+  </si>
+  <si>
+    <t>패링</t>
+  </si>
+  <si>
+    <t>보존</t>
+  </si>
+  <si>
+    <t>방어도 9</t>
+  </si>
+  <si>
+    <t>방어도 9를 얻습니다. 사용하지 않아도 턴 종료시 버려지지 않습니다.</t>
+  </si>
+  <si>
     <t>맹독의 늪</t>
   </si>
   <si>
@@ -385,9 +427,6 @@
     <t>영역/버프</t>
   </si>
   <si>
-    <t>방어도 5</t>
-  </si>
-  <si>
     <t>[인접 2칸] 내에 지정한 타일에 3턴간 유지되는 성역을 생성합니다. 플레이어 진입 시 방어도 5를 얻습니다.</t>
   </si>
   <si>
@@ -407,36 +446,6 @@
   </si>
   <si>
     <t>효과 설명</t>
-  </si>
-  <si>
-    <t>낡은 방패</t>
-  </si>
-  <si>
-    <t>기술</t>
-  </si>
-  <si>
-    <t>일반</t>
-  </si>
-  <si>
-    <t>방어도 5를 얻습니다.</t>
-  </si>
-  <si>
-    <t>무기 교체</t>
-  </si>
-  <si>
-    <t>시동</t>
-  </si>
-  <si>
-    <t>방어도 4를 얻고 이번 전투에서 사용한 특수 카드 1장을 덱으로 가져옵니다.</t>
-  </si>
-  <si>
-    <t>패링</t>
-  </si>
-  <si>
-    <t>보존</t>
-  </si>
-  <si>
-    <t>방어도 9를 얻습니다. 사용하지 않아도 턴 종료시 버려지지 않습니다.</t>
   </si>
   <si>
     <t>광전사의 피</t>
@@ -1064,16 +1073,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.63"/>
-    <col customWidth="1" min="2" max="2" width="9.13"/>
-    <col customWidth="1" min="3" max="3" width="17.0"/>
-    <col customWidth="1" min="4" max="4" width="8.25"/>
-    <col customWidth="1" min="5" max="6" width="7.13"/>
-    <col customWidth="1" min="7" max="7" width="14.5"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="10" width="18.0"/>
-    <col customWidth="1" min="11" max="11" width="90.5"/>
-    <col customWidth="1" min="12" max="12" width="16.0"/>
+    <col customWidth="1" min="1" max="1" width="7.63"/>
+    <col customWidth="1" min="2" max="2" width="10.63"/>
+    <col customWidth="1" min="3" max="3" width="9.13"/>
+    <col customWidth="1" min="4" max="4" width="17.0"/>
+    <col customWidth="1" min="5" max="5" width="8.25"/>
+    <col customWidth="1" min="6" max="7" width="7.13"/>
+    <col customWidth="1" min="8" max="8" width="14.5"/>
+    <col customWidth="1" min="9" max="9" width="8.63"/>
+    <col customWidth="1" min="10" max="11" width="18.0"/>
+    <col customWidth="1" min="12" max="12" width="90.5"/>
+    <col customWidth="1" min="13" max="13" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1118,15 @@
         <v>64</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>65</v>
+      <c r="A2" s="1">
+        <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>66</v>
@@ -1121,28 +1134,31 @@
       <c r="C2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="1">
-        <v>1.0</v>
+      <c r="D2" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I2" s="1">
         <v>6.0</v>
       </c>
-      <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>68</v>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>69</v>
+      <c r="A3" s="1">
+        <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>70</v>
@@ -1150,176 +1166,194 @@
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.0</v>
+      <c r="D3" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="E3" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1">
-        <v>2.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="1">
         <v>8.0</v>
       </c>
-      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="3" t="s">
-        <v>72</v>
+      <c r="K3" s="1"/>
+      <c r="L3" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>73</v>
+      <c r="A4" s="1">
+        <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.0</v>
+        <v>75</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E4" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1">
-        <v>1.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="1">
         <v>6.0</v>
       </c>
-      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="3" t="s">
-        <v>75</v>
+      <c r="K4" s="1"/>
+      <c r="L4" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>76</v>
+      <c r="A5" s="1">
+        <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2.0</v>
+        <v>78</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E5" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>3.0</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>5.0</v>
       </c>
-      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="3" t="s">
-        <v>78</v>
+      <c r="K5" s="1"/>
+      <c r="L5" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>79</v>
+      <c r="A6" s="1">
+        <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="1">
-        <v>1.0</v>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E6" s="1">
         <v>1.0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="F6" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="1"/>
       <c r="H6" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="1">
         <v>15.0</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="J6" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="L6" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>82</v>
+      <c r="A7" s="1">
+        <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="1">
-        <v>1.0</v>
+      <c r="D7" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E7" s="1">
         <v>1.0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="F7" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="1">
         <v>6.0</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="3" t="s">
+      <c r="J7" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="3" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>85</v>
+      <c r="A8" s="1">
+        <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2.0</v>
+        <v>87</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E8" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>8.0</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>6.0</v>
       </c>
-      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="3" t="s">
-        <v>87</v>
+      <c r="K8" s="1"/>
+      <c r="L8" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>88</v>
+      <c r="A9" s="1">
+        <v>8.0</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>89</v>
@@ -1327,59 +1361,65 @@
       <c r="C9" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="6">
-        <v>1.0</v>
+      <c r="D9" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="E9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
-        <v>1.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="1"/>
       <c r="H9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="6">
         <v>5.0</v>
       </c>
-      <c r="I9" s="5"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="5" t="s">
-        <v>91</v>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>92</v>
+      <c r="A10" s="1">
+        <v>9.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="6">
-        <v>1.0</v>
+      <c r="D10" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="E10" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6">
-        <v>1.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G10" s="1"/>
       <c r="H10" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="6">
         <v>6.0</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
         <v>94</v>
       </c>
+      <c r="L10" s="5" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>95</v>
+      <c r="A11" s="1">
+        <v>10.0</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>96</v>
@@ -1387,61 +1427,67 @@
       <c r="C11" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="6">
-        <v>1.0</v>
+      <c r="D11" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E11" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6">
-        <v>2.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G11" s="1"/>
       <c r="H11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="6">
         <v>6.0</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>99</v>
+      <c r="A12" s="1">
+        <v>11.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="6">
-        <v>1.0</v>
+      <c r="D12" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="E12" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6">
-        <v>1.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G12" s="1"/>
       <c r="H12" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="6">
         <v>5.0</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
-        <v>100</v>
-      </c>
+      <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
         <v>101</v>
       </c>
+      <c r="L12" s="5" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>102</v>
+      <c r="A13" s="1">
+        <v>12.0</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>103</v>
@@ -1449,344 +1495,187 @@
       <c r="C13" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="6">
-        <v>2.0</v>
+      <c r="D13" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="E13" s="6">
         <v>2.0</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6">
+      <c r="F13" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="6">
         <v>5.0</v>
       </c>
-      <c r="H13" s="7">
+      <c r="I13" s="7">
         <v>46300.0</v>
       </c>
-      <c r="I13" s="5"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="5" t="s">
-        <v>105</v>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>106</v>
+      <c r="A14" s="1">
+        <v>13.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.0</v>
+        <v>90</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="E14" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6">
-        <v>2.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I14" s="6">
         <v>4.0</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="J14" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K14" s="8" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="K14" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F17" s="9">
-        <v>-1.0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F18" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F19" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G19" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="20">
-      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21">
-      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22">
-      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23">
-      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24">
-      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25">
-      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26">
-      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
     </row>
     <row r="27">
-      <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="K27" s="4"/>
+      <c r="G27" s="1"/>
+      <c r="L27" s="4"/>
     </row>
     <row r="28">
-      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="K28" s="4"/>
+      <c r="G28" s="1"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29">
-      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="K29" s="4"/>
+      <c r="G29" s="1"/>
+      <c r="L29" s="4"/>
     </row>
     <row r="30">
-      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="K30" s="4"/>
+      <c r="G30" s="1"/>
+      <c r="L30" s="4"/>
     </row>
     <row r="31">
-      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="K31" s="4"/>
+      <c r="G31" s="1"/>
+      <c r="L31" s="4"/>
     </row>
     <row r="32">
-      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
     </row>
     <row r="33">
-      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
     </row>
     <row r="34">
-      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
     </row>
     <row r="35">
-      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
     </row>
     <row r="36">
-      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
     </row>
     <row r="37">
-      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
     </row>
     <row r="38">
-      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
     </row>
     <row r="39">
-      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
     </row>
     <row r="40">
-      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
     </row>
     <row r="41">
-      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
     </row>
     <row r="42">
-      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
     </row>
     <row r="43">
-      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
     </row>
     <row r="44">
-      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
     </row>
     <row r="45">
-      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
     </row>
     <row r="46">
-      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
     </row>
     <row r="47">
-      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
     </row>
     <row r="48">
-      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
     </row>
     <row r="49">
-      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
     </row>
     <row r="50">
-      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
     </row>
     <row r="51">
-      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
     </row>
     <row r="52">
-      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
     </row>
     <row r="53">
-      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
     </row>
     <row r="54">
-      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
     </row>
     <row r="55">
-      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
     </row>
     <row r="56">
-      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
     </row>
     <row r="57">
-      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1800,11 +1689,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="8.38"/>
+    <col customWidth="1" min="1" max="1" width="6.75"/>
+    <col customWidth="1" min="2" max="2" width="8.38"/>
     <col customWidth="1" min="3" max="3" width="8.25"/>
     <col customWidth="1" min="4" max="4" width="8.63"/>
-    <col customWidth="1" min="5" max="5" width="63.5"/>
-    <col customWidth="1" min="6" max="6" width="51.0"/>
+    <col customWidth="1" min="5" max="5" width="10.0"/>
+    <col customWidth="1" min="6" max="6" width="8.13"/>
+    <col customWidth="1" min="12" max="12" width="87.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1812,83 +1703,294 @@
         <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>-1.0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+    <row r="8">
+      <c r="A8" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="9">
+      <c r="A9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="C9" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="E9" s="4"/>
     </row>
     <row r="10">
       <c r="E10" s="4"/>
@@ -2052,53 +2154,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D2" s="1">
         <v>0.0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1">
         <v>2.0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">

--- a/문서함/기획/카드/카드.xlsx
+++ b/문서함/기획/카드/카드.xlsx
@@ -6,7 +6,7 @@
     <sheet state="visible" name="시트6" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="카드 용어 정리" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="카드 분류" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="카드 효과" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="상태 효과" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="공격 카드" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="기술 카드" sheetId="6" r:id="rId10"/>
     <sheet state="visible" name="능력 카드" sheetId="7" r:id="rId11"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="171">
   <si>
     <t>이름</t>
   </si>
@@ -133,13 +133,13 @@
     <t>집중 N</t>
   </si>
   <si>
-    <t>N 턴 동안 공격력 50% 증가</t>
+    <t>N 턴 동안 공격력 25% 증가</t>
   </si>
   <si>
     <t>표적 N</t>
   </si>
   <si>
-    <t>N 턴 동안 방어력 50% 감소</t>
+    <t>N 턴 동안 받는 피해 증가 50% 감소</t>
   </si>
   <si>
     <t>혼란 N</t>
@@ -163,7 +163,7 @@
     <t>출혈 N</t>
   </si>
   <si>
-    <t>N 턴 동안 턴 시작시 최대 체력 5% 피해</t>
+    <t>N 턴 동안 턴 시작시 최대 체력 3% 피해</t>
   </si>
   <si>
     <t>방어도 N</t>
@@ -175,13 +175,19 @@
     <t>중독 N</t>
   </si>
   <si>
-    <t>N 턴 동안 턴 시작 시 최대 체력 5% 피해</t>
+    <t>N 턴 동안 턴 시작 시 최대 체력 3% 피해</t>
   </si>
   <si>
     <t>부상 N</t>
   </si>
   <si>
-    <t>N 턴 동안 손패 카드 중 랜덤으로 소모 마나(코스트) 1 증가</t>
+    <t>N 턴 동안 손패 카드 중 랜덤으로 1장의 소모 마나(코스트) 1 증가</t>
+  </si>
+  <si>
+    <t>악화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[중독], </t>
   </si>
   <si>
     <t>번호</t>
@@ -358,6 +364,9 @@
     <t>일반</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>방어도 5</t>
   </si>
   <si>
@@ -437,6 +446,60 @@
   </si>
   <si>
     <t>[인접 2칸] 내에 지정한 타일에 2턴간 유지되는 빛의 웅덩이를 생성합니다. 플레이어 진입 시 즉시 5 회복, [집중 1]을 얻습니다.</t>
+  </si>
+  <si>
+    <t>약점 분석</t>
+  </si>
+  <si>
+    <t>디버프</t>
+  </si>
+  <si>
+    <t>[인접 2칸] 내에 지정한 적에게 [표적 1]을 부여합니다.</t>
+  </si>
+  <si>
+    <t>눈가림 가루</t>
+  </si>
+  <si>
+    <t>[인접 2칸] 내에 지정한 적에게 [혼란 1]을 부여합니다.</t>
+  </si>
+  <si>
+    <t>마력 사슬</t>
+  </si>
+  <si>
+    <t>고립 1, 표적 1</t>
+  </si>
+  <si>
+    <t>[인접 2칸] 내에 지정한 적에게 [고립 1]과 [표적 1]을 부여합니다.</t>
+  </si>
+  <si>
+    <t>독물</t>
+  </si>
+  <si>
+    <t>효과 수준</t>
+  </si>
+  <si>
+    <t>중독 2</t>
+  </si>
+  <si>
+    <t>[인접 2칸] 내에 지정한 적에게 [중독 2]를 부여합니다.</t>
+  </si>
+  <si>
+    <t>틱 데미지 2배</t>
+  </si>
+  <si>
+    <t>[인접 2칸] 내에 지정한 적이 [중독] 혹은 [출혈]일 경우 [악화]를 부여합니다.</t>
+  </si>
+  <si>
+    <t>톱날 무기</t>
+  </si>
+  <si>
+    <t>버프</t>
+  </si>
+  <si>
+    <t>출혈 2</t>
+  </si>
+  <si>
+    <t>다음에 사용할 카드가 [인접]카드일 경우 적에게 [출혈 2]를 추가 부여한다.</t>
   </si>
   <si>
     <t>카드 효과</t>
@@ -966,7 +1029,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="34.5"/>
+    <col customWidth="1" min="2" max="2" width="45.5"/>
     <col customWidth="1" min="3" max="3" width="25.88"/>
     <col customWidth="1" min="4" max="4" width="31.25"/>
   </cols>
@@ -1059,7 +1122,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1088,37 +1156,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -1129,13 +1197,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
@@ -1153,7 +1221,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -1161,13 +1229,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="1">
         <v>1.0</v>
@@ -1185,7 +1253,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -1193,13 +1261,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
@@ -1217,7 +1285,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
@@ -1225,13 +1293,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1">
         <v>2.0</v>
@@ -1249,7 +1317,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -1257,13 +1325,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" s="1">
         <v>1.0</v>
@@ -1279,10 +1347,10 @@
         <v>15.0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -1290,13 +1358,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1">
         <v>1.0</v>
@@ -1312,11 +1380,11 @@
         <v>6.0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -1324,13 +1392,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1">
         <v>2.0</v>
@@ -1348,7 +1416,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -1356,13 +1424,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="6">
         <v>1.0</v>
@@ -1380,7 +1448,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -1388,13 +1456,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="E10" s="6">
         <v>1.0</v>
@@ -1411,10 +1479,10 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -1422,13 +1490,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E11" s="6">
         <v>1.0</v>
@@ -1445,10 +1513,10 @@
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -1456,13 +1524,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="6">
         <v>1.0</v>
@@ -1479,10 +1547,10 @@
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1490,13 +1558,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E13" s="6">
         <v>2.0</v>
@@ -1514,7 +1582,7 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1522,13 +1590,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="6">
         <v>1.0</v>
@@ -1544,13 +1612,13 @@
         <v>4.0</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
@@ -1690,7 +1758,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="6.75"/>
-    <col customWidth="1" min="2" max="2" width="8.38"/>
+    <col customWidth="1" min="2" max="2" width="10.63"/>
     <col customWidth="1" min="3" max="3" width="8.25"/>
     <col customWidth="1" min="4" max="4" width="8.63"/>
     <col customWidth="1" min="5" max="5" width="10.0"/>
@@ -1700,37 +1768,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -1741,25 +1809,28 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G2" s="1">
         <v>1.0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -1767,25 +1838,28 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.0</v>
-      </c>
       <c r="G3" s="1">
         <v>1.0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -1793,25 +1867,28 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G4" s="1">
         <v>1.0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
@@ -1819,13 +1896,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="6">
         <v>1.0</v>
@@ -1840,14 +1917,14 @@
         <v>1.0</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -1855,13 +1932,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="6">
         <v>2.0</v>
@@ -1876,12 +1953,12 @@
         <v>1.0</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
@@ -1889,13 +1966,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="6">
         <v>1.0</v>
@@ -1914,10 +1991,10 @@
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8">
@@ -1925,13 +2002,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="6">
         <v>1.0</v>
@@ -1949,11 +2026,11 @@
         <v>0.0</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -1961,13 +2038,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="6">
         <v>2.0</v>
@@ -1985,33 +2062,228 @@
         <v>0.0</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="4"/>
+      <c r="A10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="11">
-      <c r="E11" s="4"/>
+      <c r="A11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="12">
-      <c r="E12" s="4"/>
+      <c r="A12" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
-      <c r="E13" s="4"/>
+      <c r="A13" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="14">
-      <c r="E14" s="4"/>
+      <c r="A14" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="15">
-      <c r="E15" s="4"/>
+      <c r="A15" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="16">
-      <c r="E16" s="4"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17">
       <c r="E17" s="4"/>
@@ -2145,7 +2417,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="8.38"/>
+    <col customWidth="1" min="1" max="1" width="10.88"/>
+    <col customWidth="1" min="2" max="2" width="8.38"/>
     <col customWidth="1" min="3" max="3" width="8.25"/>
     <col customWidth="1" min="4" max="4" width="8.63"/>
     <col customWidth="1" min="5" max="5" width="63.5"/>
@@ -2154,53 +2427,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D2" s="1">
         <v>0.0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="D3" s="1">
         <v>2.0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">

--- a/문서함/기획/카드/카드.xlsx
+++ b/문서함/기획/카드/카드.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="180">
   <si>
     <t>이름</t>
   </si>
@@ -139,7 +139,10 @@
     <t>표적 N</t>
   </si>
   <si>
-    <t>N 턴 동안 받는 피해 증가 50% 감소</t>
+    <t>N 턴 동안 받는 피해 50% 증가</t>
+  </si>
+  <si>
+    <t>카드 효과에 넣지 말것</t>
   </si>
   <si>
     <t>혼란 N</t>
@@ -358,10 +361,7 @@
     <t>낡은 방패</t>
   </si>
   <si>
-    <t>기술</t>
-  </si>
-  <si>
-    <t>일반</t>
+    <t>방어</t>
   </si>
   <si>
     <t>-</t>
@@ -376,21 +376,15 @@
     <t>무기 교체</t>
   </si>
   <si>
-    <t>시동</t>
-  </si>
-  <si>
     <t>방어도 4</t>
   </si>
   <si>
-    <t>방어도 4를 얻고 이번 전투에서 사용한 특수 카드 1장을 덱으로 가져옵니다.</t>
+    <t>방어도 4를 얻고 이번 전투에서 사용한 카드 한장을 가져옵니다.</t>
   </si>
   <si>
     <t>패링</t>
   </si>
   <si>
-    <t>보존</t>
-  </si>
-  <si>
     <t>방어도 9</t>
   </si>
   <si>
@@ -499,7 +493,40 @@
     <t>출혈 2</t>
   </si>
   <si>
-    <t>다음에 사용할 카드가 [인접]카드일 경우 적에게 [출혈 2]를 추가 부여한다.</t>
+    <t>다음에 사용할 카드가 [인접]카드일 경우 적에게 [출혈 2]를 추가 부여합니다.</t>
+  </si>
+  <si>
+    <t>마력 장벽</t>
+  </si>
+  <si>
+    <t>방어도 12</t>
+  </si>
+  <si>
+    <t>방어도 12를 얻습니다.</t>
+  </si>
+  <si>
+    <t>응수 자세</t>
+  </si>
+  <si>
+    <t>방어/버프</t>
+  </si>
+  <si>
+    <t>방어도 4, 집중 1</t>
+  </si>
+  <si>
+    <t>방어도 4를 획득하고, 자신에게 [집중 1]을 부여합니다.</t>
+  </si>
+  <si>
+    <t>순간 회피</t>
+  </si>
+  <si>
+    <t>방어/이동</t>
+  </si>
+  <si>
+    <t>방어도 2</t>
+  </si>
+  <si>
+    <t>[인접 1칸] 내에 자신을 이동 시키고 방어도 2를 획득합니다.</t>
   </si>
   <si>
     <t>카드 효과</t>
@@ -583,9 +610,6 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -597,6 +621,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -1058,75 +1085,77 @@
       <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1149,44 +1178,45 @@
     <col customWidth="1" min="6" max="7" width="7.13"/>
     <col customWidth="1" min="8" max="8" width="14.5"/>
     <col customWidth="1" min="9" max="9" width="8.63"/>
-    <col customWidth="1" min="10" max="11" width="18.0"/>
+    <col customWidth="1" min="10" max="10" width="18.5"/>
+    <col customWidth="1" min="11" max="11" width="18.0"/>
     <col customWidth="1" min="12" max="12" width="90.5"/>
     <col customWidth="1" min="13" max="13" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -1197,13 +1227,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
@@ -1221,7 +1251,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -1229,13 +1259,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1">
         <v>1.0</v>
@@ -1253,7 +1283,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -1261,13 +1291,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
@@ -1285,7 +1315,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -1293,13 +1323,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5" s="1">
         <v>2.0</v>
@@ -1317,7 +1347,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -1325,13 +1355,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" s="1">
         <v>1.0</v>
@@ -1347,10 +1377,10 @@
         <v>15.0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1358,13 +1388,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" s="1">
         <v>1.0</v>
@@ -1380,11 +1410,11 @@
         <v>6.0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -1392,13 +1422,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1">
         <v>2.0</v>
@@ -1416,334 +1446,334 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="D9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="5">
         <v>2.0</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="H9" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="5">
         <v>5.0</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>94</v>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="B10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="D10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="5">
         <v>2.0</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I10" s="6">
+      <c r="H10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="5">
         <v>6.0</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="J10" s="4"/>
+      <c r="K10" s="4" t="s">
         <v>97</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="D11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="5">
         <v>2.0</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="6">
+      <c r="H11" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="5">
         <v>6.0</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>101</v>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="B12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E12" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="D12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="5">
         <v>2.0</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="6">
+      <c r="H12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="5">
         <v>5.0</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L12" s="5" t="s">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4" t="s">
         <v>104</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="D13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F13" s="5">
         <v>2.0</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>5.0</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>46300.0</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
-        <v>108</v>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="B14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="5">
         <v>2.0</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I14" s="6">
+      <c r="H14" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I14" s="5">
         <v>4.0</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="8" t="s">
+      <c r="J14" s="4" t="s">
         <v>111</v>
       </c>
+      <c r="K14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="20">
-      <c r="L20" s="4"/>
+      <c r="L20" s="8"/>
     </row>
     <row r="21">
-      <c r="L21" s="4"/>
+      <c r="L21" s="8"/>
     </row>
     <row r="22">
-      <c r="L22" s="4"/>
+      <c r="L22" s="8"/>
     </row>
     <row r="23">
-      <c r="L23" s="4"/>
+      <c r="L23" s="8"/>
     </row>
     <row r="24">
-      <c r="L24" s="4"/>
+      <c r="L24" s="8"/>
     </row>
     <row r="25">
-      <c r="L25" s="4"/>
+      <c r="L25" s="8"/>
     </row>
     <row r="26">
-      <c r="L26" s="4"/>
+      <c r="L26" s="8"/>
     </row>
     <row r="27">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="L27" s="4"/>
+      <c r="L27" s="8"/>
     </row>
     <row r="28">
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="L28" s="4"/>
+      <c r="L28" s="8"/>
     </row>
     <row r="29">
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="L29" s="4"/>
+      <c r="L29" s="8"/>
     </row>
     <row r="30">
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="L30" s="4"/>
+      <c r="L30" s="8"/>
     </row>
     <row r="31">
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="L31" s="4"/>
+      <c r="L31" s="8"/>
     </row>
     <row r="32">
-      <c r="L32" s="4"/>
+      <c r="L32" s="8"/>
     </row>
     <row r="33">
-      <c r="L33" s="4"/>
+      <c r="L33" s="8"/>
     </row>
     <row r="34">
-      <c r="L34" s="4"/>
+      <c r="L34" s="8"/>
     </row>
     <row r="35">
-      <c r="L35" s="4"/>
+      <c r="L35" s="8"/>
     </row>
     <row r="36">
-      <c r="L36" s="4"/>
+      <c r="L36" s="8"/>
     </row>
     <row r="37">
-      <c r="L37" s="4"/>
+      <c r="L37" s="8"/>
     </row>
     <row r="38">
-      <c r="L38" s="4"/>
+      <c r="L38" s="8"/>
     </row>
     <row r="39">
-      <c r="L39" s="4"/>
+      <c r="L39" s="8"/>
     </row>
     <row r="40">
-      <c r="L40" s="4"/>
+      <c r="L40" s="8"/>
     </row>
     <row r="41">
-      <c r="L41" s="4"/>
+      <c r="L41" s="8"/>
     </row>
     <row r="42">
-      <c r="L42" s="4"/>
+      <c r="L42" s="8"/>
     </row>
     <row r="43">
-      <c r="L43" s="4"/>
+      <c r="L43" s="8"/>
     </row>
     <row r="44">
-      <c r="L44" s="4"/>
+      <c r="L44" s="8"/>
     </row>
     <row r="45">
-      <c r="L45" s="4"/>
+      <c r="L45" s="8"/>
     </row>
     <row r="46">
-      <c r="L46" s="4"/>
+      <c r="L46" s="8"/>
     </row>
     <row r="47">
-      <c r="L47" s="4"/>
+      <c r="L47" s="8"/>
     </row>
     <row r="48">
-      <c r="L48" s="4"/>
+      <c r="L48" s="8"/>
     </row>
     <row r="49">
-      <c r="L49" s="4"/>
+      <c r="L49" s="8"/>
     </row>
     <row r="50">
-      <c r="L50" s="4"/>
+      <c r="L50" s="8"/>
     </row>
     <row r="51">
-      <c r="L51" s="4"/>
+      <c r="L51" s="8"/>
     </row>
     <row r="52">
-      <c r="L52" s="4"/>
+      <c r="L52" s="8"/>
     </row>
     <row r="53">
-      <c r="L53" s="4"/>
+      <c r="L53" s="8"/>
     </row>
     <row r="54">
-      <c r="L54" s="4"/>
+      <c r="L54" s="8"/>
     </row>
     <row r="55">
-      <c r="L55" s="4"/>
+      <c r="L55" s="8"/>
     </row>
     <row r="56">
-      <c r="L56" s="4"/>
+      <c r="L56" s="8"/>
     </row>
     <row r="57">
-      <c r="L57" s="4"/>
+      <c r="L57" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1768,37 +1798,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -1809,12 +1839,9 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>114</v>
       </c>
       <c r="E2" s="1">
@@ -1826,6 +1853,12 @@
       <c r="G2" s="1">
         <v>1.0</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="J2" s="1" t="s">
         <v>116</v>
       </c>
@@ -1841,10 +1874,7 @@
         <v>118</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1">
         <v>1.0</v>
@@ -1855,11 +1885,17 @@
       <c r="G3" s="1">
         <v>1.0</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="J3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -1867,13 +1903,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
@@ -1884,189 +1917,195 @@
       <c r="G4" s="1">
         <v>1.0</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="B7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="5">
         <v>2.0</v>
       </c>
       <c r="G7" s="9">
         <v>-1.0</v>
       </c>
-      <c r="H7" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="6">
+      <c r="H7" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="5">
         <v>0.0</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5" t="s">
-        <v>103</v>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -2074,13 +2113,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" s="3">
         <v>1.0</v>
@@ -2098,10 +2137,10 @@
         <v>0.0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -2109,13 +2148,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3">
         <v>1.0</v>
@@ -2133,10 +2172,10 @@
         <v>0.0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12">
@@ -2144,13 +2183,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3">
         <v>2.0</v>
@@ -2168,10 +2207,10 @@
         <v>0.0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -2179,34 +2218,34 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -2214,13 +2253,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" s="3">
         <v>1.0</v>
@@ -2238,10 +2277,10 @@
         <v>0.0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
@@ -2249,13 +2288,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" s="3">
         <v>1.0</v>
@@ -2276,134 +2315,221 @@
         <v>0.0</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="E16" s="3"/>
+      <c r="L16" s="1" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="17">
-      <c r="E17" s="4"/>
+      <c r="A17" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="18">
-      <c r="E18" s="4"/>
+      <c r="A18" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="19">
-      <c r="E19" s="4"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20">
-      <c r="E20" s="4"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21">
-      <c r="E21" s="4"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22">
-      <c r="E22" s="4"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23">
-      <c r="E23" s="4"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24">
-      <c r="E24" s="4"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25">
-      <c r="E25" s="4"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26">
-      <c r="E26" s="4"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27">
-      <c r="E27" s="4"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28">
-      <c r="E28" s="4"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29">
-      <c r="E29" s="4"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30">
-      <c r="E30" s="4"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31">
-      <c r="E31" s="4"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32">
-      <c r="E32" s="4"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33">
-      <c r="E33" s="4"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34">
-      <c r="E34" s="4"/>
+      <c r="E34" s="8"/>
     </row>
     <row r="35">
-      <c r="E35" s="4"/>
+      <c r="E35" s="8"/>
     </row>
     <row r="36">
-      <c r="E36" s="4"/>
+      <c r="E36" s="8"/>
     </row>
     <row r="37">
-      <c r="E37" s="4"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38">
-      <c r="E38" s="4"/>
+      <c r="E38" s="8"/>
     </row>
     <row r="39">
-      <c r="E39" s="4"/>
+      <c r="E39" s="8"/>
     </row>
     <row r="40">
-      <c r="E40" s="4"/>
+      <c r="E40" s="8"/>
     </row>
     <row r="41">
-      <c r="E41" s="4"/>
+      <c r="E41" s="8"/>
     </row>
     <row r="42">
-      <c r="E42" s="4"/>
+      <c r="E42" s="8"/>
     </row>
     <row r="43">
-      <c r="E43" s="4"/>
+      <c r="E43" s="8"/>
     </row>
     <row r="44">
-      <c r="E44" s="4"/>
+      <c r="E44" s="8"/>
     </row>
     <row r="45">
-      <c r="E45" s="4"/>
+      <c r="E45" s="8"/>
     </row>
     <row r="46">
-      <c r="E46" s="4"/>
+      <c r="E46" s="8"/>
     </row>
     <row r="47">
-      <c r="E47" s="4"/>
+      <c r="E47" s="8"/>
     </row>
     <row r="48">
-      <c r="E48" s="4"/>
+      <c r="E48" s="8"/>
     </row>
     <row r="49">
-      <c r="E49" s="4"/>
+      <c r="E49" s="8"/>
     </row>
     <row r="50">
-      <c r="E50" s="4"/>
+      <c r="E50" s="8"/>
     </row>
     <row r="51">
-      <c r="E51" s="4"/>
+      <c r="E51" s="8"/>
     </row>
     <row r="52">
-      <c r="E52" s="4"/>
+      <c r="E52" s="8"/>
     </row>
     <row r="53">
-      <c r="E53" s="4"/>
+      <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="E54" s="4"/>
+      <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="E55" s="4"/>
+      <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="E56" s="4"/>
+      <c r="E56" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2427,53 +2553,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D2" s="1">
         <v>0.0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D3" s="1">
         <v>2.0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
@@ -2489,151 +2615,151 @@
       <c r="E7" s="3"/>
     </row>
     <row r="8">
-      <c r="E8" s="4"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9">
-      <c r="E9" s="4"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10">
-      <c r="E10" s="4"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11">
-      <c r="E11" s="4"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12">
-      <c r="E12" s="4"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13">
-      <c r="E13" s="4"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14">
-      <c r="E14" s="4"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15">
-      <c r="E15" s="4"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16">
-      <c r="E16" s="4"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17">
-      <c r="E17" s="4"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18">
-      <c r="E18" s="4"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19">
-      <c r="E19" s="4"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20">
-      <c r="E20" s="4"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21">
-      <c r="E21" s="4"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22">
-      <c r="E22" s="4"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23">
-      <c r="E23" s="4"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24">
-      <c r="E24" s="4"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25">
-      <c r="E25" s="4"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26">
-      <c r="E26" s="4"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27">
-      <c r="E27" s="4"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28">
-      <c r="E28" s="4"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29">
-      <c r="E29" s="4"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30">
-      <c r="E30" s="4"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31">
-      <c r="E31" s="4"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32">
-      <c r="E32" s="4"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33">
-      <c r="E33" s="4"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34">
-      <c r="E34" s="4"/>
+      <c r="E34" s="8"/>
     </row>
     <row r="35">
-      <c r="E35" s="4"/>
+      <c r="E35" s="8"/>
     </row>
     <row r="36">
-      <c r="E36" s="4"/>
+      <c r="E36" s="8"/>
     </row>
     <row r="37">
-      <c r="E37" s="4"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38">
-      <c r="E38" s="4"/>
+      <c r="E38" s="8"/>
     </row>
     <row r="39">
-      <c r="E39" s="4"/>
+      <c r="E39" s="8"/>
     </row>
     <row r="40">
-      <c r="E40" s="4"/>
+      <c r="E40" s="8"/>
     </row>
     <row r="41">
-      <c r="E41" s="4"/>
+      <c r="E41" s="8"/>
     </row>
     <row r="42">
-      <c r="E42" s="4"/>
+      <c r="E42" s="8"/>
     </row>
     <row r="43">
-      <c r="E43" s="4"/>
+      <c r="E43" s="8"/>
     </row>
     <row r="44">
-      <c r="E44" s="4"/>
+      <c r="E44" s="8"/>
     </row>
     <row r="45">
-      <c r="E45" s="4"/>
+      <c r="E45" s="8"/>
     </row>
     <row r="46">
-      <c r="E46" s="4"/>
+      <c r="E46" s="8"/>
     </row>
     <row r="47">
-      <c r="E47" s="4"/>
+      <c r="E47" s="8"/>
     </row>
     <row r="48">
-      <c r="E48" s="4"/>
+      <c r="E48" s="8"/>
     </row>
     <row r="49">
-      <c r="E49" s="4"/>
+      <c r="E49" s="8"/>
     </row>
     <row r="50">
-      <c r="E50" s="4"/>
+      <c r="E50" s="8"/>
     </row>
     <row r="51">
-      <c r="E51" s="4"/>
+      <c r="E51" s="8"/>
     </row>
     <row r="52">
-      <c r="E52" s="4"/>
+      <c r="E52" s="8"/>
     </row>
     <row r="53">
-      <c r="E53" s="4"/>
+      <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="E54" s="4"/>
+      <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="E55" s="4"/>
+      <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="E56" s="4"/>
+      <c r="E56" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/문서함/기획/카드/카드.xlsx
+++ b/문서함/기획/카드/카드.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="188">
   <si>
     <t>이름</t>
   </si>
@@ -169,7 +169,7 @@
     <t>N 턴 동안 턴 시작시 최대 체력 3% 피해</t>
   </si>
   <si>
-    <t>방어도 N</t>
+    <t>방어도</t>
   </si>
   <si>
     <t>N 턴 동안 임시 추가 체력</t>
@@ -244,7 +244,7 @@
     <t>인접/관통</t>
   </si>
   <si>
-    <t>상하좌우 2칸</t>
+    <t>눈꽃 2칸</t>
   </si>
   <si>
     <t>[상하좌우 2칸] 내에 [관통] 직선상에 있는 모든 적에게 8 피해를 줍니다.</t>
@@ -265,6 +265,9 @@
     <t>인접/횡베기</t>
   </si>
   <si>
+    <t>넉백</t>
+  </si>
+  <si>
     <t>[인접 1칸] 중 선택한 방향으로 [횡베기]를 합니다. 적중한 적에게 5피해를 주며 뒤로 1칸 밀어냅니다.</t>
   </si>
   <si>
@@ -280,9 +283,6 @@
     <t>방패 가격</t>
   </si>
   <si>
-    <t>방어도</t>
-  </si>
-  <si>
     <t>[인접 1칸] 내에 선택한 타일 [단일 타격]로 6피해를 줍니다. 피해를 준 수치만큼 [방어도]를 획득합니다.</t>
   </si>
   <si>
@@ -322,9 +322,6 @@
     <t>투사/관통</t>
   </si>
   <si>
-    <t>X자 2칸</t>
-  </si>
-  <si>
     <t>[X자 2칸] 중 지정한 방향으로 [관통]을 하여 모든 적을 공격합니다. 적중한 모든 적에게 [표적 1]과 6 피해를 줍니다.</t>
   </si>
   <si>
@@ -343,9 +340,6 @@
     <t>투사/폭팔</t>
   </si>
   <si>
-    <t>눈꽃 모양 2칸</t>
-  </si>
-  <si>
     <t>[눈꽃 모양 2칸] 내에 지정한 타일에 대상을 맞추고 폭발합니다. 대상은 10 피해를 받고 주변 적들에게는 스플래시 5 피해를 줍니다.</t>
   </si>
   <si>
@@ -358,12 +352,42 @@
     <t>[인접 2칸] 내에 적을 견제합니다. 대상에게 [고립 1]과 [다음 카드 인접 카드 강화], 4 피해를 줍니다.</t>
   </si>
   <si>
+    <t>육중한 압박</t>
+  </si>
+  <si>
+    <t>방어도 * 1.5</t>
+  </si>
+  <si>
+    <t>[단일] 현재 보유한 [방어도]의 1.5배 만큼 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>구석 몰이</t>
+  </si>
+  <si>
+    <t>[단일] 4피해. 대상의 뒤가 [벽]이나 [다른 적]이면 8 추가 피해</t>
+  </si>
+  <si>
+    <t>궁지 타격</t>
+  </si>
+  <si>
+    <t>[단일] 적을 밀치고 7피해. 대상이 [벽]을 등지고 있다면 0코스트</t>
+  </si>
+  <si>
+    <t>불도저</t>
+  </si>
+  <si>
+    <t>[돌진] 지정 방향 2칸 전진. 경로상 모든 적 1칸 밀치고 4피해</t>
+  </si>
+  <si>
     <t>낡은 방패</t>
   </si>
   <si>
     <t>방어</t>
   </si>
   <si>
+    <t>본인</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -529,34 +553,34 @@
     <t>[인접 1칸] 내에 자신을 이동 시키고 방어도 2를 획득합니다.</t>
   </si>
   <si>
-    <t>카드 효과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">소모 마나 </t>
+    <t>압사</t>
+  </si>
+  <si>
+    <t>표적 2, 벽쿵시 행동 불가</t>
+  </si>
+  <si>
+    <t>단일 적에게 [표적 2] 부여. 대상이 다음 턴 종료 전까지 밀쳐져서 벽에 부딪히면 행동 불가</t>
+  </si>
+  <si>
+    <t>철벽의 태세</t>
+  </si>
+  <si>
+    <t>방어도 6</t>
+  </si>
+  <si>
+    <t>방어도 6 획득. 다음 턴 시작 시 방어도가 1이상이면 내 [인접 1칸]의 적 1칸 밀치기</t>
   </si>
   <si>
     <t>효과 설명</t>
   </si>
   <si>
-    <t>광전사의 피</t>
+    <t>공성 전차</t>
   </si>
   <si>
     <t>능력</t>
   </si>
   <si>
-    <t>혈채</t>
-  </si>
-  <si>
-    <t>체력 3를 소모하며, 전투가 끝날때 까지 힘 3을 얻습니다. 공격 카드를 사용할때 마다 체력 3씩 소모합니다.</t>
-  </si>
-  <si>
-    <t>전술의 대가</t>
-  </si>
-  <si>
-    <t>소멸</t>
-  </si>
-  <si>
-    <t>시동 효과를 발동할 때마다 방어도 3을 얻습니다.</t>
+    <t>전투 종료까지, 적을 벽에 [밀치기]로 충돌시킬 때마다 공정 7피해 및 방어도 4 획득</t>
   </si>
 </sst>
 </file>
@@ -566,7 +590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m, d"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -582,13 +606,30 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -597,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -610,23 +651,41 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1264,7 +1323,7 @@
       <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>75</v>
       </c>
       <c r="E3" s="1">
@@ -1345,9 +1404,11 @@
         <v>5.0</v>
       </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="L5" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -1355,7 +1416,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>70</v>
@@ -1377,10 +1438,10 @@
         <v>15.0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -1388,7 +1449,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>70</v>
@@ -1410,7 +1471,7 @@
         <v>6.0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="3" t="s">
@@ -1453,31 +1514,31 @@
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="6">
         <v>2.0</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="H9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="6">
         <v>5.0</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1485,33 +1546,33 @@
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="6">
         <v>2.0</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="6">
         <v>6.0</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4" t="s">
+      <c r="J10" s="5"/>
+      <c r="K10" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="5" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1519,261 +1580,386 @@
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46300.0</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>46300.0</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="4" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>46120.0</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F14" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="E18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I18" s="1">
         <v>4.0</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>112</v>
+      <c r="K18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="20">
-      <c r="L20" s="8"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21">
-      <c r="L21" s="8"/>
+      <c r="B21" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="L21" s="12"/>
     </row>
     <row r="22">
-      <c r="L22" s="8"/>
+      <c r="B22" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="L22" s="12"/>
     </row>
     <row r="23">
-      <c r="L23" s="8"/>
+      <c r="L23" s="12"/>
     </row>
     <row r="24">
-      <c r="L24" s="8"/>
+      <c r="L24" s="12"/>
     </row>
     <row r="25">
-      <c r="L25" s="8"/>
+      <c r="L25" s="12"/>
     </row>
     <row r="26">
-      <c r="L26" s="8"/>
+      <c r="L26" s="12"/>
     </row>
     <row r="27">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="12"/>
     </row>
     <row r="28">
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="12"/>
     </row>
     <row r="29">
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="12"/>
     </row>
     <row r="30">
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="L30" s="8"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31">
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="L31" s="8"/>
+      <c r="L31" s="12"/>
     </row>
     <row r="32">
-      <c r="L32" s="8"/>
+      <c r="L32" s="12"/>
     </row>
     <row r="33">
-      <c r="L33" s="8"/>
+      <c r="L33" s="12"/>
     </row>
     <row r="34">
-      <c r="L34" s="8"/>
+      <c r="L34" s="12"/>
     </row>
     <row r="35">
-      <c r="L35" s="8"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36">
-      <c r="L36" s="8"/>
+      <c r="L36" s="12"/>
     </row>
     <row r="37">
-      <c r="L37" s="8"/>
+      <c r="L37" s="12"/>
     </row>
     <row r="38">
-      <c r="L38" s="8"/>
+      <c r="L38" s="12"/>
     </row>
     <row r="39">
-      <c r="L39" s="8"/>
+      <c r="L39" s="12"/>
     </row>
     <row r="40">
-      <c r="L40" s="8"/>
+      <c r="L40" s="12"/>
     </row>
     <row r="41">
-      <c r="L41" s="8"/>
+      <c r="L41" s="12"/>
     </row>
     <row r="42">
-      <c r="L42" s="8"/>
+      <c r="L42" s="12"/>
     </row>
     <row r="43">
-      <c r="L43" s="8"/>
+      <c r="L43" s="12"/>
     </row>
     <row r="44">
-      <c r="L44" s="8"/>
+      <c r="L44" s="12"/>
     </row>
     <row r="45">
-      <c r="L45" s="8"/>
+      <c r="L45" s="12"/>
     </row>
     <row r="46">
-      <c r="L46" s="8"/>
+      <c r="L46" s="12"/>
     </row>
     <row r="47">
-      <c r="L47" s="8"/>
+      <c r="L47" s="12"/>
     </row>
     <row r="48">
-      <c r="L48" s="8"/>
+      <c r="L48" s="12"/>
     </row>
     <row r="49">
-      <c r="L49" s="8"/>
+      <c r="L49" s="12"/>
     </row>
     <row r="50">
-      <c r="L50" s="8"/>
+      <c r="L50" s="12"/>
     </row>
     <row r="51">
-      <c r="L51" s="8"/>
+      <c r="L51" s="12"/>
     </row>
     <row r="52">
-      <c r="L52" s="8"/>
+      <c r="L52" s="12"/>
     </row>
     <row r="53">
-      <c r="L53" s="8"/>
+      <c r="L53" s="12"/>
     </row>
     <row r="54">
-      <c r="L54" s="8"/>
+      <c r="L54" s="12"/>
     </row>
     <row r="55">
-      <c r="L55" s="8"/>
+      <c r="L55" s="12"/>
     </row>
     <row r="56">
-      <c r="L56" s="8"/>
+      <c r="L56" s="12"/>
     </row>
     <row r="57">
-      <c r="L57" s="8"/>
+      <c r="L57" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1787,13 +1973,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="6.75"/>
+    <col customWidth="1" min="1" max="1" width="8.13"/>
     <col customWidth="1" min="2" max="2" width="10.63"/>
-    <col customWidth="1" min="3" max="3" width="8.25"/>
+    <col customWidth="1" min="3" max="3" width="12.63"/>
     <col customWidth="1" min="4" max="4" width="8.63"/>
-    <col customWidth="1" min="5" max="5" width="10.0"/>
+    <col customWidth="1" min="5" max="5" width="21.5"/>
     <col customWidth="1" min="6" max="6" width="8.13"/>
-    <col customWidth="1" min="12" max="12" width="87.5"/>
+    <col customWidth="1" min="12" max="12" width="86.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1839,31 +2025,34 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G2" s="1">
         <v>1.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
@@ -1871,31 +2060,34 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.0</v>
+        <v>121</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G3" s="1">
         <v>1.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
@@ -1903,209 +2095,212 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>114</v>
+      <c r="D4" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G4" s="1">
         <v>1.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="E5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="6">
         <v>3.0</v>
       </c>
-      <c r="H5" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>127</v>
+      <c r="H5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4" t="s">
-        <v>131</v>
+      <c r="E6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="6">
         <v>2.0</v>
       </c>
       <c r="G7" s="9">
         <v>-1.0</v>
       </c>
-      <c r="H7" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="H7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="6">
         <v>0.0</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4" t="s">
-        <v>104</v>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="E8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="6">
         <v>3.0</v>
       </c>
-      <c r="H8" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="H8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="6">
         <v>0.0</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4" t="s">
-        <v>137</v>
+      <c r="J8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="E9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="6">
         <v>0.0</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
-        <v>140</v>
+      <c r="J9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -2113,10 +2308,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>94</v>
@@ -2140,7 +2335,7 @@
         <v>97</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -2148,10 +2343,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>94</v>
@@ -2172,10 +2367,10 @@
         <v>0.0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
@@ -2183,10 +2378,10 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>94</v>
@@ -2207,10 +2402,10 @@
         <v>0.0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -2218,10 +2413,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>94</v>
@@ -2239,13 +2434,13 @@
         <v>1.0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -2256,7 +2451,7 @@
         <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>94</v>
@@ -2268,7 +2463,7 @@
         <v>2.0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H14" s="1">
         <v>1.0</v>
@@ -2277,10 +2472,10 @@
         <v>0.0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15">
@@ -2288,19 +2483,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="E15" s="3">
         <v>1.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G15" s="1">
         <v>1.0</v>
@@ -2315,10 +2510,10 @@
         <v>0.0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
@@ -2326,31 +2521,34 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E16" s="3">
         <v>2.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G16" s="1">
         <v>1.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17">
@@ -2358,31 +2556,34 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E17" s="3">
         <v>1.0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G17" s="1">
         <v>1.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18">
@@ -2390,10 +2591,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E18" s="3">
         <v>0.0</v>
@@ -2402,134 +2606,201 @@
         <v>1.0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H18" s="1">
         <v>1.0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19">
-      <c r="E19" s="8"/>
+      <c r="A19" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="20">
-      <c r="E20" s="8"/>
+      <c r="A20" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="21">
-      <c r="E21" s="8"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22">
-      <c r="E22" s="8"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23">
-      <c r="E23" s="8"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24">
-      <c r="E24" s="8"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25">
-      <c r="E25" s="8"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26">
-      <c r="E26" s="8"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27">
-      <c r="E27" s="8"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28">
-      <c r="E28" s="8"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29">
-      <c r="E29" s="8"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30">
-      <c r="E30" s="8"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31">
-      <c r="E31" s="8"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32">
-      <c r="E32" s="8"/>
+      <c r="E32" s="12"/>
     </row>
     <row r="33">
-      <c r="E33" s="8"/>
+      <c r="E33" s="12"/>
     </row>
     <row r="34">
-      <c r="E34" s="8"/>
+      <c r="E34" s="12"/>
     </row>
     <row r="35">
-      <c r="E35" s="8"/>
+      <c r="E35" s="12"/>
     </row>
     <row r="36">
-      <c r="E36" s="8"/>
+      <c r="E36" s="12"/>
     </row>
     <row r="37">
-      <c r="E37" s="8"/>
+      <c r="E37" s="12"/>
     </row>
     <row r="38">
-      <c r="E38" s="8"/>
+      <c r="E38" s="12"/>
     </row>
     <row r="39">
-      <c r="E39" s="8"/>
+      <c r="E39" s="12"/>
     </row>
     <row r="40">
-      <c r="E40" s="8"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41">
-      <c r="E41" s="8"/>
+      <c r="E41" s="12"/>
     </row>
     <row r="42">
-      <c r="E42" s="8"/>
+      <c r="E42" s="12"/>
     </row>
     <row r="43">
-      <c r="E43" s="8"/>
+      <c r="E43" s="12"/>
     </row>
     <row r="44">
-      <c r="E44" s="8"/>
+      <c r="E44" s="12"/>
     </row>
     <row r="45">
-      <c r="E45" s="8"/>
+      <c r="E45" s="12"/>
     </row>
     <row r="46">
-      <c r="E46" s="8"/>
+      <c r="E46" s="12"/>
     </row>
     <row r="47">
-      <c r="E47" s="8"/>
+      <c r="E47" s="12"/>
     </row>
     <row r="48">
-      <c r="E48" s="8"/>
+      <c r="E48" s="12"/>
     </row>
     <row r="49">
-      <c r="E49" s="8"/>
+      <c r="E49" s="12"/>
     </row>
     <row r="50">
-      <c r="E50" s="8"/>
+      <c r="E50" s="12"/>
     </row>
     <row r="51">
-      <c r="E51" s="8"/>
+      <c r="E51" s="12"/>
     </row>
     <row r="52">
-      <c r="E52" s="8"/>
+      <c r="E52" s="12"/>
     </row>
     <row r="53">
-      <c r="E53" s="8"/>
+      <c r="E53" s="12"/>
     </row>
     <row r="54">
-      <c r="E54" s="8"/>
+      <c r="E54" s="12"/>
     </row>
     <row r="55">
-      <c r="E55" s="8"/>
+      <c r="E55" s="12"/>
     </row>
     <row r="56">
-      <c r="E56" s="8"/>
+      <c r="E56" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2543,64 +2814,49 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="2" max="2" width="8.38"/>
-    <col customWidth="1" min="3" max="3" width="8.25"/>
-    <col customWidth="1" min="4" max="4" width="8.63"/>
+    <col customWidth="1" min="1" max="2" width="10.88"/>
+    <col customWidth="1" min="3" max="3" width="8.38"/>
+    <col customWidth="1" min="4" max="4" width="8.25"/>
     <col customWidth="1" min="5" max="5" width="63.5"/>
     <col customWidth="1" min="6" max="6" width="51.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>173</v>
+      <c r="A2" s="1">
+        <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>179</v>
-      </c>
+      <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="E4" s="3"/>
@@ -2615,151 +2871,151 @@
       <c r="E7" s="3"/>
     </row>
     <row r="8">
-      <c r="E8" s="8"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9">
-      <c r="E9" s="8"/>
+      <c r="E9" s="12"/>
     </row>
     <row r="10">
-      <c r="E10" s="8"/>
+      <c r="E10" s="12"/>
     </row>
     <row r="11">
-      <c r="E11" s="8"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12">
-      <c r="E12" s="8"/>
+      <c r="E12" s="12"/>
     </row>
     <row r="13">
-      <c r="E13" s="8"/>
+      <c r="E13" s="12"/>
     </row>
     <row r="14">
-      <c r="E14" s="8"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15">
-      <c r="E15" s="8"/>
+      <c r="E15" s="12"/>
     </row>
     <row r="16">
-      <c r="E16" s="8"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17">
-      <c r="E17" s="8"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18">
-      <c r="E18" s="8"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19">
-      <c r="E19" s="8"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20">
-      <c r="E20" s="8"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21">
-      <c r="E21" s="8"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22">
-      <c r="E22" s="8"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23">
-      <c r="E23" s="8"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24">
-      <c r="E24" s="8"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25">
-      <c r="E25" s="8"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26">
-      <c r="E26" s="8"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27">
-      <c r="E27" s="8"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28">
-      <c r="E28" s="8"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29">
-      <c r="E29" s="8"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30">
-      <c r="E30" s="8"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31">
-      <c r="E31" s="8"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32">
-      <c r="E32" s="8"/>
+      <c r="E32" s="12"/>
     </row>
     <row r="33">
-      <c r="E33" s="8"/>
+      <c r="E33" s="12"/>
     </row>
     <row r="34">
-      <c r="E34" s="8"/>
+      <c r="E34" s="12"/>
     </row>
     <row r="35">
-      <c r="E35" s="8"/>
+      <c r="E35" s="12"/>
     </row>
     <row r="36">
-      <c r="E36" s="8"/>
+      <c r="E36" s="12"/>
     </row>
     <row r="37">
-      <c r="E37" s="8"/>
+      <c r="E37" s="12"/>
     </row>
     <row r="38">
-      <c r="E38" s="8"/>
+      <c r="E38" s="12"/>
     </row>
     <row r="39">
-      <c r="E39" s="8"/>
+      <c r="E39" s="12"/>
     </row>
     <row r="40">
-      <c r="E40" s="8"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41">
-      <c r="E41" s="8"/>
+      <c r="E41" s="12"/>
     </row>
     <row r="42">
-      <c r="E42" s="8"/>
+      <c r="E42" s="12"/>
     </row>
     <row r="43">
-      <c r="E43" s="8"/>
+      <c r="E43" s="12"/>
     </row>
     <row r="44">
-      <c r="E44" s="8"/>
+      <c r="E44" s="12"/>
     </row>
     <row r="45">
-      <c r="E45" s="8"/>
+      <c r="E45" s="12"/>
     </row>
     <row r="46">
-      <c r="E46" s="8"/>
+      <c r="E46" s="12"/>
     </row>
     <row r="47">
-      <c r="E47" s="8"/>
+      <c r="E47" s="12"/>
     </row>
     <row r="48">
-      <c r="E48" s="8"/>
+      <c r="E48" s="12"/>
     </row>
     <row r="49">
-      <c r="E49" s="8"/>
+      <c r="E49" s="12"/>
     </row>
     <row r="50">
-      <c r="E50" s="8"/>
+      <c r="E50" s="12"/>
     </row>
     <row r="51">
-      <c r="E51" s="8"/>
+      <c r="E51" s="12"/>
     </row>
     <row r="52">
-      <c r="E52" s="8"/>
+      <c r="E52" s="12"/>
     </row>
     <row r="53">
-      <c r="E53" s="8"/>
+      <c r="E53" s="12"/>
     </row>
     <row r="54">
-      <c r="E54" s="8"/>
+      <c r="E54" s="12"/>
     </row>
     <row r="55">
-      <c r="E55" s="8"/>
+      <c r="E55" s="12"/>
     </row>
     <row r="56">
-      <c r="E56" s="8"/>
+      <c r="E56" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/문서함/기획/카드/카드.xlsx
+++ b/문서함/기획/카드/카드.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="195">
   <si>
     <t>이름</t>
   </si>
@@ -130,12 +130,18 @@
     <t>효과</t>
   </si>
   <si>
+    <t>기획 문서</t>
+  </si>
+  <si>
     <t>집중 N</t>
   </si>
   <si>
     <t>N 턴 동안 공격력 25% 증가</t>
   </si>
   <si>
+    <t>상태효과 기획서</t>
+  </si>
+  <si>
     <t>표적 N</t>
   </si>
   <si>
@@ -193,6 +199,24 @@
     <t xml:space="preserve">[중독], </t>
   </si>
   <si>
+    <t>압사 대기 N</t>
+  </si>
+  <si>
+    <t>N턴 동안 밀쳐져서 충돌 시 [행동 불가 N] 부여</t>
+  </si>
+  <si>
+    <t>행동 불가 N]</t>
+  </si>
+  <si>
+    <t>N턴 동안 이동 불가, 몬스터의 공격 및 스킬 행동 불가</t>
+  </si>
+  <si>
+    <t>차징</t>
+  </si>
+  <si>
+    <t>다음 턴 시작 시 방어도가 1 이상이면 내 [인접 1칸]의 모든 적 1칸 밀치기</t>
+  </si>
+  <si>
     <t>번호</t>
   </si>
   <si>
@@ -226,6 +250,9 @@
     <t>적 효과 부여</t>
   </si>
   <si>
+    <t>설명 (인게임 내 설명 텍스트)</t>
+  </si>
+  <si>
     <t>타격</t>
   </si>
   <si>
@@ -235,7 +262,7 @@
     <t>인접 1칸</t>
   </si>
   <si>
-    <t>[인접 1칸] 내에 선택한 타일 [단일 타격] 로 6피해를 줍니다.</t>
+    <t>인접한 적 하나에게 6의 피해를 줍니다.</t>
   </si>
   <si>
     <t>찌르기</t>
@@ -247,7 +274,7 @@
     <t>눈꽃 2칸</t>
   </si>
   <si>
-    <t>[상하좌우 2칸] 내에 [관통] 직선상에 있는 모든 적에게 8 피해를 줍니다.</t>
+    <t>직선 방향으로 2칸 내의 모든 적을 꿰뚫어 8의 피해를 줍니다. 벽에 막히면 그 뒤는 공격할 수 없습니다.</t>
   </si>
   <si>
     <t>어깨치기</t>
@@ -256,7 +283,7 @@
     <t>인접/돌진</t>
   </si>
   <si>
-    <t>[인접 1칸] 중 1칸 이동합니다. 향한 방향에 있는 [돌진] 적에게 6 피해를 줍니다.</t>
+    <t>인접한 타일 중 한칸으로 돌진한 뒤, 바로 앞의 적에게 6의 피해를 줍니다.</t>
   </si>
   <si>
     <t>휩쓸기</t>
@@ -268,7 +295,7 @@
     <t>넉백</t>
   </si>
   <si>
-    <t>[인접 1칸] 중 선택한 방향으로 [횡베기]를 합니다. 적중한 적에게 5피해를 주며 뒤로 1칸 밀어냅니다.</t>
+    <t>전방 3칸 범위의 모든 적에게 5의 피해를 주고 1칸 뒤로 밀쳐냅니다. 밀려난 위치에 장애물이 있으면 추가 피해를 줍니다.</t>
   </si>
   <si>
     <t>처형</t>
@@ -277,13 +304,13 @@
     <t>혼란 1</t>
   </si>
   <si>
-    <t>[인접 1칸] 내에 선택한 타일 [단일 타격] 로치명적인 피해를 줍니다. 사용 후 플레이어는 해당 턴 동안 [혼란 1]을 부여합니다.</t>
+    <t>인접한 적에게 15의 강력한 피해를 주지만, 사용 후 자신은 1턴 동안 [혼란] 상태가 되어 공격력이 절반으로 감소합니다.</t>
   </si>
   <si>
     <t>방패 가격</t>
   </si>
   <si>
-    <t>[인접 1칸] 내에 선택한 타일 [단일 타격]로 6피해를 줍니다. 피해를 준 수치만큼 [방어도]를 획득합니다.</t>
+    <t>인접한 적에게 6의 피해를 주고, 입힌 피해량만큼 자신의 [방어도]를 올립니다.</t>
   </si>
   <si>
     <t>회전 베기</t>
@@ -292,7 +319,7 @@
     <t>인접/전방위</t>
   </si>
   <si>
-    <t>[인접 1칸] 몸을 빠르게 회전하여 [전방위]를 타격하여 6 피해를 줍니다.</t>
+    <t>자신을 둘러싼 주변 8칸의 모든 적에게 동시에 6의 피해를 줍니다.</t>
   </si>
   <si>
     <t>사격</t>
@@ -304,7 +331,7 @@
     <t>인접 2칸</t>
   </si>
   <si>
-    <t>[인접 2칸] 내의 적 하나를 조준하여 공격합니다. 대상에게 5 피해를 줍니다.</t>
+    <t>2칸 내의 적 하나에게 5의 피해를 줍니다. 벽 너머의 적도 공격할 수 있습니다.</t>
   </si>
   <si>
     <t>정밀 사격</t>
@@ -313,7 +340,7 @@
     <t>표적 1</t>
   </si>
   <si>
-    <t>[인접 2칸] 내의 적 하나를 조준하여 공격합니다. 대상에게 [표적 1]과 6 피해를 줍니다.</t>
+    <t>적에게 6의 피해를 주고, 1턴 동안 받는 피해가 50% 증가하는 [표적] 상태로 만듭니다.</t>
   </si>
   <si>
     <t>관통 화살</t>
@@ -322,7 +349,7 @@
     <t>투사/관통</t>
   </si>
   <si>
-    <t>[X자 2칸] 중 지정한 방향으로 [관통]을 하여 모든 적을 공격합니다. 적중한 모든 적에게 [표적 1]과 6 피해를 줍니다.</t>
+    <t>눈꽃 방향(가로, 세로, 대각선 8방향) 2칸 내의 모든 적에게 6의 피해를 주고 [표적] 상태를 부여합니다.</t>
   </si>
   <si>
     <t>그림자 묶기</t>
@@ -331,7 +358,7 @@
     <t>고립 1</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 적 하나를 조준하여 공격합니다. 대상에게 [고립 1]과 5 피해를 줍니다.</t>
+    <t>적에게 5의 피해를 주고 1턴 동안 이동할 수 없는 [고립] 상태로 만듭니다.</t>
   </si>
   <si>
     <t>마력 폭탄</t>
@@ -340,7 +367,7 @@
     <t>투사/폭팔</t>
   </si>
   <si>
-    <t>[눈꽃 모양 2칸] 내에 지정한 타일에 대상을 맞추고 폭발합니다. 대상은 10 피해를 받고 주변 적들에게는 스플래시 5 피해를 줍니다.</t>
+    <t>대상에게 10의 피해를 주고, 주변 X자 범위에 5의 스플래시 피해를 줍니다.</t>
   </si>
   <si>
     <t>견제 사격</t>
@@ -349,7 +376,7 @@
     <t>다음 인접 카드 50% 증가</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 적을 견제합니다. 대상에게 [고립 1]과 [다음 카드 인접 카드 강화], 4 피해를 줍니다.</t>
+    <t>8방향 2칸 내의 모든 적에게 4의 피해와 [고립]을 부여합니다. 사용 후 다음에 쓰는 [인접] 카드의 피해량이 50% 증가합니다.</t>
   </si>
   <si>
     <t>육중한 압박</t>
@@ -358,25 +385,25 @@
     <t>방어도 * 1.5</t>
   </si>
   <si>
-    <t>[단일] 현재 보유한 [방어도]의 1.5배 만큼 피해를 줍니다.</t>
+    <t>인접한 적에게 현재 내 [방어도] 수치의 1.5배만큼 피해를 줍니다. (방어도는 소모되지 않음)</t>
   </si>
   <si>
     <t>구석 몰이</t>
   </si>
   <si>
-    <t>[단일] 4피해. 대상의 뒤가 [벽]이나 [다른 적]이면 8 추가 피해</t>
+    <t>인접한 적에게 4의 피해를 줍니다. 적의 뒤가 벽이나 다른 개체로 막혀 있다면 8의 추가 피해를 입힙니다.</t>
   </si>
   <si>
     <t>궁지 타격</t>
   </si>
   <si>
-    <t>[단일] 적을 밀치고 7피해. 대상이 [벽]을 등지고 있다면 0코스트</t>
+    <t>인접한 적에게 7의 피해를 줍니다. 대상의 뒤가 벽이라면 코스트가 0이 됩니다.</t>
   </si>
   <si>
     <t>불도저</t>
   </si>
   <si>
-    <t>[돌진] 지정 방향 2칸 전진. 경로상 모든 적 1칸 밀치고 4피해</t>
+    <t>지정 방향으로 2칸 돌진하며 경로상의 적을 밀어내고 4+4의 피해를 줍니다.</t>
   </si>
   <si>
     <t>낡은 방패</t>
@@ -394,7 +421,7 @@
     <t>방어도 5</t>
   </si>
   <si>
-    <t>방어도 5를 얻습니다.</t>
+    <t>즉시 5의 [방어도]를 얻습니다.</t>
   </si>
   <si>
     <t>무기 교체</t>
@@ -403,7 +430,7 @@
     <t>방어도 4</t>
   </si>
   <si>
-    <t>방어도 4를 얻고 이번 전투에서 사용한 카드 한장을 가져옵니다.</t>
+    <t>즉시 4의 [방어도]를 얻고, 버린 카드 더미에서 원하는 카드 1장을 손패로 가져옵니다.</t>
   </si>
   <si>
     <t>패링</t>
@@ -412,7 +439,7 @@
     <t>방어도 9</t>
   </si>
   <si>
-    <t>방어도 9를 얻습니다. 사용하지 않아도 턴 종료시 버려지지 않습니다.</t>
+    <t>즉시 9의 [방어도]를 얻습니다. 턴 종료 시 사라지지 않고 손패에 유지됩니다.</t>
   </si>
   <si>
     <t>맹독의 늪</t>
@@ -424,7 +451,7 @@
     <t>턴 당 3</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 타일에 3턴간 유지되는 독 늪을 생성합니다. 진입 시 4피해를 입고 [혼란 1]을 얻습니다.</t>
+    <t>3턴 동안 유지되는 독 장판을 생성합니다. 진입 시 4, 매 턴 3의 피해를 주며 적을 [혼란] 상태로 만듭니다.</t>
   </si>
   <si>
     <t>타오르는 잿불</t>
@@ -436,7 +463,7 @@
     <t>턴 당 8</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 타일에 2턴간 유지되는 불길을 생성합니다. 진입 시 8피해를 입습니다.</t>
+    <t>2턴 동안 강력한 불길을 일으켜 진입 및 턴 시작 시 8의 피해를 줍니다.</t>
   </si>
   <si>
     <t>거미줄 함정</t>
@@ -445,7 +472,7 @@
     <t>영역/CC</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 타일에 끈적한 거미줄을 설치합니다. 진입 시 [고립 1]을 부여하고 사라집니다.</t>
+    <t>밟으면 파괴되며 즉시 대상을 [고립] 상태로 만드는 함정을 설치합니다.</t>
   </si>
   <si>
     <t>성역의 문양</t>
@@ -454,7 +481,7 @@
     <t>영역/버프</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 타일에 3턴간 유지되는 성역을 생성합니다. 플레이어 진입 시 방어도 5를 얻습니다.</t>
+    <t>3턴 동안 유지되는 문양을 새깁니다. 플레이어가 이 위를 밟으면 5의 [방어도]를 얻습니다.</t>
   </si>
   <si>
     <t>빛의 웅덩이</t>
@@ -463,7 +490,7 @@
     <t>5 회복, 집중 1</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 타일에 2턴간 유지되는 빛의 웅덩이를 생성합니다. 플레이어 진입 시 즉시 5 회복, [집중 1]을 얻습니다.</t>
+    <t>2턴 동안 유지되는 빛의 영역을 만듭니다. 이 위에서 턴을 시작하거나 진입 시 체력을 5 회복하고 [집중] 상태가 됩니다.</t>
   </si>
   <si>
     <t>약점 분석</t>
@@ -472,13 +499,13 @@
     <t>디버프</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 적에게 [표적 1]을 부여합니다.</t>
+    <t>적에게 [표적 1] 상태를 부여합니다.</t>
   </si>
   <si>
     <t>눈가림 가루</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 적에게 [혼란 1]을 부여합니다.</t>
+    <t>적에게 [혼란 1] 상태를 부여합니다.</t>
   </si>
   <si>
     <t>마력 사슬</t>
@@ -487,7 +514,7 @@
     <t>고립 1, 표적 1</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 적에게 [고립 1]과 [표적 1]을 부여합니다.</t>
+    <t>적에게 [고립 1]과 [표적 1]을 동시에 부여합니다.</t>
   </si>
   <si>
     <t>독물</t>
@@ -499,25 +526,22 @@
     <t>중독 2</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 적에게 [중독 2]를 부여합니다.</t>
+    <t>적에게 [중독 2] 상태를 부여합니다.</t>
   </si>
   <si>
     <t>틱 데미지 2배</t>
   </si>
   <si>
-    <t>[인접 2칸] 내에 지정한 적이 [중독] 혹은 [출혈]일 경우 [악화]를 부여합니다.</t>
+    <t>이미 중독이나 출혈 상태인 적에게 사용하면, 해당 상태 이상의 지속 피해량을 2배로 강화합니다.</t>
   </si>
   <si>
     <t>톱날 무기</t>
   </si>
   <si>
-    <t>버프</t>
-  </si>
-  <si>
     <t>출혈 2</t>
   </si>
   <si>
-    <t>다음에 사용할 카드가 [인접]카드일 경우 적에게 [출혈 2]를 추가 부여합니다.</t>
+    <t>다음에 사용하는 [인접] 공격 카드에 [출혈 2] 효과를 부여합니다.</t>
   </si>
   <si>
     <t>마력 장벽</t>
@@ -526,7 +550,7 @@
     <t>방어도 12</t>
   </si>
   <si>
-    <t>방어도 12를 얻습니다.</t>
+    <t>즉시 12의 높은 [방어도]를 얻습니다.</t>
   </si>
   <si>
     <t>응수 자세</t>
@@ -538,19 +562,19 @@
     <t>방어도 4, 집중 1</t>
   </si>
   <si>
-    <t>방어도 4를 획득하고, 자신에게 [집중 1]을 부여합니다.</t>
+    <t>4의 [방어도]를 얻고, [집중 1]을 획득합니다.</t>
   </si>
   <si>
     <t>순간 회피</t>
   </si>
   <si>
-    <t>방어/이동</t>
+    <t>이동/방어</t>
   </si>
   <si>
     <t>방어도 2</t>
   </si>
   <si>
-    <t>[인접 1칸] 내에 자신을 이동 시키고 방어도 2를 획득합니다.</t>
+    <t>인접한 빈칸으로 이동하고 2의 [방어도]를 얻습니다.</t>
   </si>
   <si>
     <t>압사</t>
@@ -559,7 +583,7 @@
     <t>표적 2, 벽쿵시 행동 불가</t>
   </si>
   <si>
-    <t>단일 적에게 [표적 2] 부여. 대상이 다음 턴 종료 전까지 밀쳐져서 벽에 부딪히면 행동 불가</t>
+    <t>적에게 [표적 2]와 [압사 대기 2]를 부여합니다. 이 상태의 적이 밀쳐져서 충돌하면 즉시 다음 행동이 봉쇄되는 [행동 불가] 상태가 됩니다.</t>
   </si>
   <si>
     <t>철벽의 태세</t>
@@ -568,10 +592,7 @@
     <t>방어도 6</t>
   </si>
   <si>
-    <t>방어도 6 획득. 다음 턴 시작 시 방어도가 1이상이면 내 [인접 1칸]의 적 1칸 밀치기</t>
-  </si>
-  <si>
-    <t>효과 설명</t>
+    <t>6의 [방어도]를 얻습니다. 다음 턴 시작 시 방어도가 1 이상 남아있다면 인접한 모든 적을 1칸 밀쳐냅니다.</t>
   </si>
   <si>
     <t>공성 전차</t>
@@ -580,7 +601,7 @@
     <t>능력</t>
   </si>
   <si>
-    <t>전투 종료까지, 적을 벽에 [밀치기]로 충돌시킬 때마다 공정 7피해 및 방어도 4 획득</t>
+    <t>이번 전투 동안 적이 벽에 충돌할 때마다 적에게 7의 피해를 주고, 자신은 4의 [방어도]를 얻습니다. 사용 후 소멸합니다.</t>
   </si>
 </sst>
 </file>
@@ -590,7 +611,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m, d"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -603,21 +624,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5A6BD"/>
+        <bgColor rgb="FFD5A6BD"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -627,8 +666,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6D7A8"/>
-        <bgColor rgb="FFB6D7A8"/>
+        <fgColor rgb="FFB4A7D6"/>
+        <bgColor rgb="FFB4A7D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -638,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -651,26 +696,38 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -678,13 +735,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1115,9 +1169,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="45.5"/>
+    <col customWidth="1" min="2" max="2" width="58.75"/>
     <col customWidth="1" min="3" max="3" width="25.88"/>
-    <col customWidth="1" min="4" max="4" width="31.25"/>
+    <col customWidth="1" min="4" max="4" width="17.75"/>
+    <col customWidth="1" min="5" max="5" width="25.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1127,98 +1182,134 @@
       <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="E2"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1244,55 +1335,55 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>1</v>
+      <c r="D1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>69</v>
+      <c r="B2" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
@@ -1310,21 +1401,21 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
+      <c r="B3" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>75</v>
+        <v>83</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="E3" s="1">
         <v>1.0</v>
@@ -1341,22 +1432,22 @@
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="3" t="s">
-        <v>76</v>
+      <c r="L3" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>77</v>
+      <c r="B4" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
@@ -1373,22 +1464,22 @@
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="3" t="s">
-        <v>79</v>
+      <c r="L4" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E5" s="1">
         <v>2.0</v>
@@ -1405,24 +1496,24 @@
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>84</v>
+      <c r="B6" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E6" s="1">
         <v>1.0</v>
@@ -1438,24 +1529,24 @@
         <v>15.0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>87</v>
+      <c r="B7" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E7" s="1">
         <v>1.0</v>
@@ -1471,25 +1562,25 @@
         <v>6.0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="3" t="s">
-        <v>88</v>
+      <c r="L7" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>89</v>
+      <c r="B8" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1">
         <v>2.0</v>
@@ -1506,210 +1597,210 @@
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="3" t="s">
-        <v>91</v>
+      <c r="L8" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="B9" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="11">
         <v>2.0</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="H9" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="11">
         <v>5.0</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>95</v>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="B10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="11">
         <v>2.0</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I10" s="6">
+      <c r="H10" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="11">
         <v>6.0</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>98</v>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="B11" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="11">
         <v>2.0</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="6">
+      <c r="H11" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="11">
         <v>6.0</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>101</v>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="D12" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="11">
         <v>2.0</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="6">
+      <c r="H12" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="11">
         <v>5.0</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>104</v>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="B13" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="F13" s="11">
         <v>2.0</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="6">
+      <c r="H13" s="11">
         <v>5.0</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="13">
         <v>46300.0</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
-        <v>107</v>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="B14" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="11">
         <v>2.0</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I14" s="6">
+      <c r="H14" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="I14" s="11">
         <v>4.0</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>110</v>
+      <c r="J14" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -1717,13 +1808,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1">
         <v>1.0</v>
@@ -1735,10 +1826,10 @@
         <v>1.0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -1746,13 +1837,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E16" s="1">
         <v>1.0</v>
@@ -1763,11 +1854,11 @@
       <c r="H16" s="1">
         <v>1.0</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="15">
         <v>46120.0</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -1775,13 +1866,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1">
         <v>1.0</v>
@@ -1793,10 +1884,10 @@
         <v>1.0</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
@@ -1804,13 +1895,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E18" s="1">
         <v>2.0</v>
@@ -1825,141 +1916,135 @@
         <v>4.0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
-      <c r="L20" s="12"/>
+      <c r="L20" s="16"/>
     </row>
     <row r="21">
-      <c r="B21" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="L21" s="12"/>
+      <c r="L21" s="16"/>
     </row>
     <row r="22">
-      <c r="B22" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="L22" s="12"/>
+      <c r="L22" s="16"/>
     </row>
     <row r="23">
-      <c r="L23" s="12"/>
+      <c r="L23" s="16"/>
     </row>
     <row r="24">
-      <c r="L24" s="12"/>
+      <c r="L24" s="16"/>
     </row>
     <row r="25">
-      <c r="L25" s="12"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26">
-      <c r="L26" s="12"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="L27" s="12"/>
+      <c r="L27" s="16"/>
     </row>
     <row r="28">
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="L28" s="12"/>
+      <c r="L28" s="16"/>
     </row>
     <row r="29">
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="L29" s="12"/>
+      <c r="L29" s="16"/>
     </row>
     <row r="30">
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="L30" s="12"/>
+      <c r="L30" s="16"/>
     </row>
     <row r="31">
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="L31" s="12"/>
+      <c r="L31" s="16"/>
     </row>
     <row r="32">
-      <c r="L32" s="12"/>
+      <c r="L32" s="16"/>
     </row>
     <row r="33">
-      <c r="L33" s="12"/>
+      <c r="L33" s="16"/>
     </row>
     <row r="34">
-      <c r="L34" s="12"/>
+      <c r="L34" s="16"/>
     </row>
     <row r="35">
-      <c r="L35" s="12"/>
+      <c r="L35" s="16"/>
     </row>
     <row r="36">
-      <c r="L36" s="12"/>
+      <c r="L36" s="16"/>
     </row>
     <row r="37">
-      <c r="L37" s="12"/>
+      <c r="L37" s="16"/>
     </row>
     <row r="38">
-      <c r="L38" s="12"/>
+      <c r="L38" s="16"/>
     </row>
     <row r="39">
-      <c r="L39" s="12"/>
+      <c r="L39" s="16"/>
     </row>
     <row r="40">
-      <c r="L40" s="12"/>
+      <c r="L40" s="16"/>
     </row>
     <row r="41">
-      <c r="L41" s="12"/>
+      <c r="L41" s="16"/>
     </row>
     <row r="42">
-      <c r="L42" s="12"/>
+      <c r="L42" s="16"/>
     </row>
     <row r="43">
-      <c r="L43" s="12"/>
+      <c r="L43" s="16"/>
     </row>
     <row r="44">
-      <c r="L44" s="12"/>
+      <c r="L44" s="16"/>
     </row>
     <row r="45">
-      <c r="L45" s="12"/>
+      <c r="L45" s="16"/>
     </row>
     <row r="46">
-      <c r="L46" s="12"/>
+      <c r="L46" s="16"/>
     </row>
     <row r="47">
-      <c r="L47" s="12"/>
+      <c r="L47" s="16"/>
     </row>
     <row r="48">
-      <c r="L48" s="12"/>
+      <c r="L48" s="16"/>
     </row>
     <row r="49">
-      <c r="L49" s="12"/>
+      <c r="L49" s="16"/>
     </row>
     <row r="50">
-      <c r="L50" s="12"/>
+      <c r="L50" s="16"/>
     </row>
     <row r="51">
-      <c r="L51" s="12"/>
+      <c r="L51" s="16"/>
     </row>
     <row r="52">
-      <c r="L52" s="12"/>
+      <c r="L52" s="16"/>
     </row>
     <row r="53">
-      <c r="L53" s="12"/>
+      <c r="L53" s="16"/>
     </row>
     <row r="54">
-      <c r="L54" s="12"/>
+      <c r="L54" s="16"/>
     </row>
     <row r="55">
-      <c r="L55" s="12"/>
+      <c r="L55" s="16"/>
     </row>
     <row r="56">
-      <c r="L56" s="12"/>
+      <c r="L56" s="16"/>
     </row>
     <row r="57">
-      <c r="L57" s="12"/>
+      <c r="L57" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1976,345 +2061,345 @@
     <col customWidth="1" min="1" max="1" width="8.13"/>
     <col customWidth="1" min="2" max="2" width="10.63"/>
     <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="8.63"/>
-    <col customWidth="1" min="5" max="5" width="21.5"/>
+    <col customWidth="1" min="4" max="4" width="14.63"/>
+    <col customWidth="1" min="5" max="5" width="6.75"/>
     <col customWidth="1" min="6" max="6" width="8.13"/>
     <col customWidth="1" min="12" max="12" width="86.75"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>1</v>
+      <c r="D1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>120</v>
+      <c r="B2" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G2" s="1">
         <v>1.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>126</v>
+      <c r="B3" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="13">
+        <v>131</v>
+      </c>
+      <c r="E3" s="18">
         <v>0.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G3" s="1">
         <v>1.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>129</v>
+      <c r="B4" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E4" s="1">
         <v>1.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G4" s="1">
         <v>1.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="H5" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>135</v>
+      <c r="L5" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>139</v>
+      <c r="B6" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G6" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="H6" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="B7" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G7" s="14">
         <v>-1.0</v>
       </c>
-      <c r="H7" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="6">
+      <c r="H7" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="11">
         <v>0.0</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>142</v>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="B8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="11">
         <v>3.0</v>
       </c>
-      <c r="H8" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="6">
+      <c r="H8" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="11">
         <v>0.0</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>145</v>
+      <c r="J8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="B9" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="11">
         <v>0.0</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>148</v>
+      <c r="J9" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>149</v>
+      <c r="B10" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E10" s="3">
         <v>1.0</v>
@@ -2332,24 +2417,24 @@
         <v>0.0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>152</v>
+      <c r="B11" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E11" s="3">
         <v>1.0</v>
@@ -2367,24 +2452,24 @@
         <v>0.0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>154</v>
+      <c r="B12" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3">
         <v>2.0</v>
@@ -2402,24 +2487,24 @@
         <v>0.0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>157</v>
+      <c r="B13" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E13" s="3">
         <v>1.0</v>
@@ -2434,27 +2519,27 @@
         <v>1.0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>56</v>
+      <c r="B14" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3">
         <v>1.0</v>
@@ -2463,7 +2548,7 @@
         <v>2.0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H14" s="1">
         <v>1.0</v>
@@ -2472,33 +2557,33 @@
         <v>0.0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
         <v>14.0</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>163</v>
+      <c r="B15" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E15" s="3">
         <v>1.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G15" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="1">
         <v>1.0</v>
@@ -2506,98 +2591,95 @@
       <c r="I15" s="1">
         <v>0.0</v>
       </c>
-      <c r="J15" s="1">
-        <v>0.0</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
         <v>15.0</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>167</v>
+      <c r="B16" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E16" s="3">
         <v>2.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G16" s="1">
         <v>1.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
         <v>16.0</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>170</v>
+      <c r="B17" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E17" s="3">
         <v>1.0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G17" s="1">
         <v>1.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
         <v>17.0</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>174</v>
+      <c r="B18" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E18" s="3">
         <v>0.0</v>
@@ -2606,19 +2688,19 @@
         <v>1.0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H18" s="1">
         <v>1.0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19">
@@ -2626,13 +2708,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E19" s="3">
         <v>2.0</v>
@@ -2650,10 +2732,10 @@
         <v>0.0</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="20">
@@ -2661,37 +2743,37 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E20" s="3">
         <v>1.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>183</v>
+        <v>91</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="21">
@@ -2701,106 +2783,106 @@
       <c r="E22" s="3"/>
     </row>
     <row r="23">
-      <c r="E23" s="12"/>
+      <c r="E23" s="16"/>
     </row>
     <row r="24">
-      <c r="E24" s="12"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="25">
-      <c r="E25" s="12"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="26">
-      <c r="E26" s="12"/>
+      <c r="E26" s="16"/>
     </row>
     <row r="27">
-      <c r="E27" s="12"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28">
-      <c r="E28" s="12"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29">
-      <c r="E29" s="12"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30">
-      <c r="E30" s="12"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31">
-      <c r="E31" s="12"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32">
-      <c r="E32" s="12"/>
+      <c r="E32" s="16"/>
     </row>
     <row r="33">
-      <c r="E33" s="12"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34">
-      <c r="E34" s="12"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="35">
-      <c r="E35" s="12"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="36">
-      <c r="E36" s="12"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37">
-      <c r="E37" s="12"/>
+      <c r="E37" s="16"/>
     </row>
     <row r="38">
-      <c r="E38" s="12"/>
+      <c r="E38" s="16"/>
     </row>
     <row r="39">
-      <c r="E39" s="12"/>
+      <c r="E39" s="16"/>
     </row>
     <row r="40">
-      <c r="E40" s="12"/>
+      <c r="E40" s="16"/>
     </row>
     <row r="41">
-      <c r="E41" s="12"/>
+      <c r="E41" s="16"/>
     </row>
     <row r="42">
-      <c r="E42" s="12"/>
+      <c r="E42" s="16"/>
     </row>
     <row r="43">
-      <c r="E43" s="12"/>
+      <c r="E43" s="16"/>
     </row>
     <row r="44">
-      <c r="E44" s="12"/>
+      <c r="E44" s="16"/>
     </row>
     <row r="45">
-      <c r="E45" s="12"/>
+      <c r="E45" s="16"/>
     </row>
     <row r="46">
-      <c r="E46" s="12"/>
+      <c r="E46" s="16"/>
     </row>
     <row r="47">
-      <c r="E47" s="12"/>
+      <c r="E47" s="16"/>
     </row>
     <row r="48">
-      <c r="E48" s="12"/>
+      <c r="E48" s="16"/>
     </row>
     <row r="49">
-      <c r="E49" s="12"/>
+      <c r="E49" s="16"/>
     </row>
     <row r="50">
-      <c r="E50" s="12"/>
+      <c r="E50" s="16"/>
     </row>
     <row r="51">
-      <c r="E51" s="12"/>
+      <c r="E51" s="16"/>
     </row>
     <row r="52">
-      <c r="E52" s="12"/>
+      <c r="E52" s="16"/>
     </row>
     <row r="53">
-      <c r="E53" s="12"/>
+      <c r="E53" s="16"/>
     </row>
     <row r="54">
-      <c r="E54" s="12"/>
+      <c r="E54" s="16"/>
     </row>
     <row r="55">
-      <c r="E55" s="12"/>
+      <c r="E55" s="16"/>
     </row>
     <row r="56">
-      <c r="E56" s="12"/>
+      <c r="E56" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2822,20 +2904,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>184</v>
+      <c r="A1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -2843,16 +2925,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D2" s="1">
         <v>2.0</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>187</v>
+      <c r="E2" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="3">
@@ -2871,151 +2953,151 @@
       <c r="E7" s="3"/>
     </row>
     <row r="8">
-      <c r="E8" s="12"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9">
-      <c r="E9" s="12"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10">
-      <c r="E10" s="12"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11">
-      <c r="E11" s="12"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12">
-      <c r="E12" s="12"/>
+      <c r="E12" s="16"/>
     </row>
     <row r="13">
-      <c r="E13" s="12"/>
+      <c r="E13" s="16"/>
     </row>
     <row r="14">
-      <c r="E14" s="12"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15">
-      <c r="E15" s="12"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16">
-      <c r="E16" s="12"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17">
-      <c r="E17" s="12"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18">
-      <c r="E18" s="12"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19">
-      <c r="E19" s="12"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20">
-      <c r="E20" s="12"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21">
-      <c r="E21" s="12"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22">
-      <c r="E22" s="12"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23">
-      <c r="E23" s="12"/>
+      <c r="E23" s="16"/>
     </row>
     <row r="24">
-      <c r="E24" s="12"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="25">
-      <c r="E25" s="12"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="26">
-      <c r="E26" s="12"/>
+      <c r="E26" s="16"/>
     </row>
     <row r="27">
-      <c r="E27" s="12"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28">
-      <c r="E28" s="12"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29">
-      <c r="E29" s="12"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30">
-      <c r="E30" s="12"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31">
-      <c r="E31" s="12"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32">
-      <c r="E32" s="12"/>
+      <c r="E32" s="16"/>
     </row>
     <row r="33">
-      <c r="E33" s="12"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34">
-      <c r="E34" s="12"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="35">
-      <c r="E35" s="12"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="36">
-      <c r="E36" s="12"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37">
-      <c r="E37" s="12"/>
+      <c r="E37" s="16"/>
     </row>
     <row r="38">
-      <c r="E38" s="12"/>
+      <c r="E38" s="16"/>
     </row>
     <row r="39">
-      <c r="E39" s="12"/>
+      <c r="E39" s="16"/>
     </row>
     <row r="40">
-      <c r="E40" s="12"/>
+      <c r="E40" s="16"/>
     </row>
     <row r="41">
-      <c r="E41" s="12"/>
+      <c r="E41" s="16"/>
     </row>
     <row r="42">
-      <c r="E42" s="12"/>
+      <c r="E42" s="16"/>
     </row>
     <row r="43">
-      <c r="E43" s="12"/>
+      <c r="E43" s="16"/>
     </row>
     <row r="44">
-      <c r="E44" s="12"/>
+      <c r="E44" s="16"/>
     </row>
     <row r="45">
-      <c r="E45" s="12"/>
+      <c r="E45" s="16"/>
     </row>
     <row r="46">
-      <c r="E46" s="12"/>
+      <c r="E46" s="16"/>
     </row>
     <row r="47">
-      <c r="E47" s="12"/>
+      <c r="E47" s="16"/>
     </row>
     <row r="48">
-      <c r="E48" s="12"/>
+      <c r="E48" s="16"/>
     </row>
     <row r="49">
-      <c r="E49" s="12"/>
+      <c r="E49" s="16"/>
     </row>
     <row r="50">
-      <c r="E50" s="12"/>
+      <c r="E50" s="16"/>
     </row>
     <row r="51">
-      <c r="E51" s="12"/>
+      <c r="E51" s="16"/>
     </row>
     <row r="52">
-      <c r="E52" s="12"/>
+      <c r="E52" s="16"/>
     </row>
     <row r="53">
-      <c r="E53" s="12"/>
+      <c r="E53" s="16"/>
     </row>
     <row r="54">
-      <c r="E54" s="12"/>
+      <c r="E54" s="16"/>
     </row>
     <row r="55">
-      <c r="E55" s="12"/>
+      <c r="E55" s="16"/>
     </row>
     <row r="56">
-      <c r="E56" s="12"/>
+      <c r="E56" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/문서함/기획/카드/카드.xlsx
+++ b/문서함/기획/카드/카드.xlsx
@@ -205,7 +205,7 @@
     <t>N턴 동안 밀쳐져서 충돌 시 [행동 불가 N] 부여</t>
   </si>
   <si>
-    <t>행동 불가 N]</t>
+    <t>행동 불가 N</t>
   </si>
   <si>
     <t>N턴 동안 이동 불가, 몬스터의 공격 및 스킬 행동 불가</t>
